--- a/Result/profitability/2483.xlsx
+++ b/Result/profitability/2483.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>0.075</v>
+        <v>0.08875</v>
       </c>
       <c r="N2" t="n">
-        <v>11.89625</v>
+        <v>12.0975</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08499999999999999</v>
+        <v>0.13125</v>
       </c>
       <c r="N3" t="n">
-        <v>12.63375</v>
+        <v>13.275</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.39</v>
       </c>
       <c r="M4" t="n">
-        <v>0.14875</v>
+        <v>0.20125</v>
       </c>
       <c r="N4" t="n">
-        <v>13.95125</v>
+        <v>14.775</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1625</v>
+        <v>0.07875</v>
       </c>
       <c r="N5" t="n">
-        <v>13.4425</v>
+        <v>14.2025</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0075</v>
+        <v>0.04749999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>12.3725</v>
+        <v>12.9325</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0025</v>
+        <v>0.045</v>
       </c>
       <c r="N7" t="n">
-        <v>13.455</v>
+        <v>14.215</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.47</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0725</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>15.835</v>
+        <v>16.05375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.22</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08124999999999999</v>
+        <v>0.08125</v>
       </c>
       <c r="N9" t="n">
         <v>17.04</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>566</v>
+      </c>
+      <c r="D75" t="n">
+        <v>481</v>
+      </c>
+      <c r="E75" t="n">
+        <v>85</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="G75" t="n">
+        <v>16</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.80%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>28</v>
+      </c>
+      <c r="K75" t="n">
+        <v>28</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.12625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.015</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1322751322751323</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7282608695652174</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.6831460674157304</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
